--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260706.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260706.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.33%</t>
+          <t>11.52%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.81%</t>
+          <t>10.00%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>8.88%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.47%</t>
+          <t>7.40%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>5.27%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>109,890</t>
+          <t>51,874</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.46%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>51,874</t>
+          <t>109,890</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>4.04%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1100,24 +1100,24 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>32,234</t>
+          <t>5,210</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,44 +1129,44 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>5,210</t>
+          <t>23,566</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>23,566</t>
+          <t>32,234</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>29,189</t>
+          <t>21,926</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>21,926</t>
+          <t>29,189</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1254,95 +1254,95 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,533</t>
+          <t>14,031</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>79,486</t>
+          <t>9,533</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,031</t>
+          <t>11,272</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>11,272</t>
+          <t>79,486</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>97,662,036</t>
+          <t>114,538,769</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
